--- a/docs/testing/test_cases_defects_dalakov.xlsx
+++ b/docs/testing/test_cases_defects_dalakov.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Сводка" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Тест-кейсы'!$A$4:$K$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Тест-кейсы'!$A$4:$K$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Дефекты'!$A$4:$K$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -58,17 +58,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF9C4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FFCDD2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFE0B2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF9C4"/>
       </patternFill>
     </fill>
   </fills>
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -511,7 +511,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Автор: Далаков Аслан, 251-952    Дата прогона: 23.09.2026    Окружение: Windows 11, Qt 6.11.1 MinGW 64-bit, сервер echoServer (порт 33333), ветка feature/dalakov</t>
+          <t>Автор: Далаков Аслан, 251-952    Дата прогона: 23.09.2026    Окружение: Windows 11, Qt 6.11.1 MinGW 64-bit, сервер echoServer (порт 33333); GUI-прогон — pywinauto (UI Automation)</t>
         </is>
       </c>
     </row>
@@ -713,12 +713,12 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>NEWTON ERROR: нужно 5 чисел + подсказка по формату</t>
+          <t>NEWTON ERROR: нужно 5 или 6 чисел + подсказка по формату</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>NEWTON ERROR: нужно 5 чисел: c3 c2 c1 c0 x0 + строка «Формат: …»</t>
+          <t>NEWTON ERROR: нужно 5 или 6 чисел: c3 c2 c1 c0 x0 [f'(x0)] + строка «Формат: …»</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Кнопка «Вариант 4: Ньютон»</t>
+          <t>Кнопка «Вариант 4: Ньютон», f'(x0) задано</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -1136,24 +1136,28 @@
       <c r="E15" s="3" t="inlineStr">
         <is>
           <t>1. Нажать «Вариант 4: Ньютон»
-2. Оставить значения по умолчанию
+2. Оставить значения по умолчанию (галочка «Задать f'(x0) вручную» стоит)
 3. OK</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>c3=1, c2=0, c1=−2, c0=−5, x0=2</t>
+          <t>c3=1, c2=0, c1=−2, c0=−5, x0=2, f'(x0)=10</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Окно «Метод Ньютона» с x1 = 2.1, запись в журнале</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr"/>
-      <c r="I15" s="5" t="inlineStr">
-        <is>
-          <t>Not run</t>
+          <t>Окно «Метод Ньютона»: f'(x0) = 10 (задано), x1 = 2.1</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>f'(x0) = 10 (задано), x1 = x0 - f(x0)/f'(x0) = 2.1, NEWTON OK x1=2.1 (скриншот 03_newton_result.png)</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1201,10 +1205,14 @@
           <t>«Задание 4 отменено»; «Статистика» показывает статистику сервера (не ошибку)</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr"/>
-      <c r="I16" s="5" t="inlineStr">
-        <is>
-          <t>Not run</t>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Окно «Статистика»: === СТАТИСТИКА СЕРВЕРА ===, ошибки нет</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1217,80 +1225,243 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
+          <t>TC-20</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Вариант 4 / клиент</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Кнопка «Вариант 4: Ньютон», f'(x0) по формуле</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Клиент и сервер запущены, вход выполнен</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>1. «Вариант 4: Ньютон»
+2. Снять галочку «Задать f'(x0) вручную»
+3. OK</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>c3=1, c2=0, c1=−2, c0=−5, x0=2</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>Сервер сам считает f'(x0) = 10, x1 = 2.1, пометки «(задано)» нет</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>f'(x0) = 10, x1 = 2.1, пометки «(задано)» нет</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>TC-21</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Вариант 4 / клиент</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Кнопка «Задание 4 (Ньютон)» — правильный ответ</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Клиент и сервер запущены, вход выполнен</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>1. «Задание 4»
+2. Вычислить x1 по условию
+3. Ввести ответ, OK</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>задание x³ + 3x² − x − 8, x0 = −1 → x1 = −2.25</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>✅ ПРАВИЛЬНО, «1 правильных из 1»</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>✅ ПРАВИЛЬНО! x1 = -2.2500, «Ваша статистика: 1 правильных из 1» (скриншот 05_task4_result.png)</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>TC-22</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Вариант 4 / сервер</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>NEWTON с заданной f'(x0), не совпадающей с формулой</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Сервер запущен, пользователь вошёл в систему</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>1. Отправить NEWTON с 6-м аргументом</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>NEWTON 1 0 -2 -5 2 5</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>Шаг по заданному f'(x0) = 5: x1 = 2.2; предупреждение, что по формуле f'(x0) = 10</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>«ВНИМАНИЕ: по формуле f'(x0) = 10, заданное значение отличается», NEWTON OK x1=2.2 (юнит-тест commandWithDerivative)</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
           <t>TC-13</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>Авторизация / сервер</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>Вход по email</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>Пользователь t@t.ru / tc зарегистрирован</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>1. LOGIN
 2. t@t.ru
 3. pw1234</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="F20" s="3" t="inlineStr">
         <is>
           <t>email вместо логина</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="G20" s="3" t="inlineStr">
         <is>
           <t>«Вход выполнен успешно! Добро пожаловать, tc!»</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr">
+      <c r="H20" s="3" t="inlineStr">
         <is>
           <t>«Вход выполнен успешно! Добро пожаловать, tc!»</t>
         </is>
       </c>
-      <c r="I17" s="4" t="inlineStr">
+      <c r="I20" s="4" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
-      <c r="J17" s="3" t="inlineStr">
+      <c r="J20" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="K17" s="3" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="K20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>TC-14</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>Авторизация / клиент</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>Регистрация через окно по подписям полей</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>Клиент запущен</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E21" s="3" t="inlineStr">
         <is>
           <t>1. В поле «Email» ввести a@b.ru
 2. В поле «Логин» ввести aslan
@@ -1298,328 +1469,328 @@
 4. Войти как aslan</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t>a@b.ru / aslan / pass123</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="G21" s="3" t="inlineStr">
         <is>
           <t>Пользователь aslan с email a@b.ru, вход по логину aslan успешен</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>Email и логин меняются местами (см. authregform.cpp: loginEdit → email, emailEdit → login)</t>
-        </is>
-      </c>
-      <c r="I18" s="6" t="inlineStr">
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Email и логин меняются местами (authregform.cpp: loginEdit → email, emailEdit → login); при входе по полю «Логин» окно пишет «Введите логин и пароль!» — подтверждено автоматическим прогоном GUI</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
         <is>
           <t>Failed</t>
         </is>
       </c>
-      <c r="J18" s="3" t="inlineStr">
+      <c r="J21" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="K18" s="3" t="inlineStr">
+      <c r="K21" s="3" t="inlineStr">
         <is>
           <t>BUG-01</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>TC-15</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>Сервер / задания</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>Команда после TASK1 без ответа</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>Сервер запущен, пользователь вошёл в систему</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>1. TASK1
 2. Не отвечать, отправить STATS</t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="F22" s="3" t="inlineStr">
         <is>
           <t>STATS</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr">
+      <c r="G22" s="3" t="inlineStr">
         <is>
           <t>Выполняется STATS (или задание отменяется)</t>
         </is>
       </c>
-      <c r="H19" s="3" t="inlineStr">
+      <c r="H22" s="3" t="inlineStr">
         <is>
           <t>«Ошибка: введите число!» — STATS принят как ответ</t>
         </is>
       </c>
-      <c r="I19" s="6" t="inlineStr">
+      <c r="I22" s="5" t="inlineStr">
         <is>
           <t>Failed</t>
         </is>
       </c>
-      <c r="J19" s="3" t="inlineStr">
+      <c r="J22" s="3" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="K19" s="3" t="inlineStr">
+      <c r="K22" s="3" t="inlineStr">
         <is>
           <t>BUG-02</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>TC-16</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>Сервер / игра</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>Сохранение игровой статистики</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>Сервер запущен, пользователь вошёл в систему</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="E23" s="3" t="inlineStr">
         <is>
           <t>1. STARTGAME
 2. Угадать число (GUESS)
 3. GAMESTATS</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="F23" s="3" t="inlineStr">
         <is>
           <t>двоичный поиск 1..100</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="G23" s="3" t="inlineStr">
         <is>
           <t>Сыграно партий: 1, Всего угадано: 1</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr">
+      <c r="H23" s="3" t="inlineStr">
         <is>
           <t>Число угадано за 7 попыток, но GAMESTATS: 0 / 0 / 0</t>
         </is>
       </c>
-      <c r="I20" s="6" t="inlineStr">
+      <c r="I23" s="5" t="inlineStr">
         <is>
           <t>Failed</t>
         </is>
       </c>
-      <c r="J20" s="3" t="inlineStr">
+      <c r="J23" s="3" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="K20" s="3" t="inlineStr">
+      <c r="K23" s="3" t="inlineStr">
         <is>
           <t>BUG-03</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>TC-17</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>Сервер / таймер</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>Простой авторизованного пользователя 60 с</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t>Сервер запущен, пользователь вошёл в систему</t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="E24" s="3" t="inlineStr">
         <is>
           <t>1. Войти
 2. Ничего не отправлять 61 с</t>
         </is>
       </c>
-      <c r="F21" s="3" t="inlineStr">
+      <c r="F24" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr">
+      <c r="G24" s="3" t="inlineStr">
         <is>
           <t>Сессия сохраняется, лишних сообщений нет</t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr">
+      <c r="H24" s="3" t="inlineStr">
         <is>
           <t>«Время ожидания истекло. Начните заново.» + меню гостя, хотя вход сохранён</t>
         </is>
       </c>
-      <c r="I21" s="6" t="inlineStr">
+      <c r="I24" s="5" t="inlineStr">
         <is>
           <t>Failed</t>
         </is>
       </c>
-      <c r="J21" s="3" t="inlineStr">
+      <c r="J24" s="3" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="K21" s="3" t="inlineStr">
+      <c r="K24" s="3" t="inlineStr">
         <is>
           <t>BUG-04</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>TC-18</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>Клиент / задания</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>Текст заданий 1 и 2 в журнале</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t>Вход выполнен</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="E25" s="3" t="inlineStr">
         <is>
           <t>1. Нажать «Задание 1»
 2. Сравнить текст журнала и текст сервера</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr">
+      <c r="F25" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr">
+      <c r="G25" s="3" t="inlineStr">
         <is>
           <t>Журнал показывает то же задание, что прислал сервер</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
+      <c r="H25" s="3" t="inlineStr">
         <is>
           <t>Журнал: «x^2 - 4 = 0», сервер: случайное линейное уравнение (mainwindow.cpp)</t>
         </is>
       </c>
-      <c r="I22" s="6" t="inlineStr">
+      <c r="I25" s="5" t="inlineStr">
         <is>
           <t>Failed</t>
         </is>
       </c>
-      <c r="J22" s="3" t="inlineStr">
+      <c r="J25" s="3" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="K22" s="3" t="inlineStr">
+      <c r="K25" s="3" t="inlineStr">
         <is>
           <t>BUG-05</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>TC-19</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>Юнит-тесты</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>Прогон tests/tests.pro</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>Qt 6 установлен</t>
         </is>
       </c>
-      <c r="E23" s="3" t="inlineStr">
+      <c r="E26" s="3" t="inlineStr">
         <is>
           <t>1. qmake tests.pro &amp;&amp; make
 2. unit_tests</t>
         </is>
       </c>
-      <c r="F23" s="3" t="inlineStr">
+      <c r="F26" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G23" s="3" t="inlineStr">
+      <c r="G26" s="3" t="inlineStr">
         <is>
           <t>0 failed, код возврата 0</t>
         </is>
       </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>TestNewton 26 passed, TestDatabase 14 passed, TestFunctionClient 9 passed, exit 0</t>
-        </is>
-      </c>
-      <c r="I23" s="4" t="inlineStr">
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>TestNewton 27, TestDatabase 12, TestFunctionClient 7 тестов — все passed, exit 0</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
-      <c r="J23" s="3" t="inlineStr">
+      <c r="J26" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="K23" s="3" t="inlineStr"/>
+      <c r="K26" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:K23"/>
+  <autoFilter ref="A4:K26"/>
   <dataValidations count="1">
-    <dataValidation sqref="I5 I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 I21 I22 I23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I5 I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 I21 I22 I23 I24 I25 I26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Passed,Failed,Not run,Blocked"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1731,7 +1902,7 @@
           <t>Окно входа: поля «Email» и «Логин» перепутаны в коде</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>Major</t>
         </is>
@@ -1743,7 +1914,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Windows 11, Qt 6.11.1 MinGW 64-bit, сервер echoServer (порт 33333), ветка feature/dalakov</t>
+          <t>Windows 11, Qt 6.11.1 MinGW 64-bit, сервер echoServer (порт 33333); GUI-прогон — pywinauto (UI Automation)</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -1790,7 +1961,7 @@
           <t>После TASK1/TASK2 любая следующая команда считается ответом</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>Major</t>
         </is>
@@ -1802,7 +1973,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Windows 11, Qt 6.11.1 MinGW 64-bit, сервер echoServer (порт 33333), ветка feature/dalakov</t>
+          <t>Windows 11, Qt 6.11.1 MinGW 64-bit, сервер echoServer (порт 33333); GUI-прогон — pywinauto (UI Automation)</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -1849,7 +2020,7 @@
           <t>Игровая статистика не сохраняется (GAMESTATS всегда 0)</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>Major</t>
         </is>
@@ -1861,7 +2032,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Windows 11, Qt 6.11.1 MinGW 64-bit, сервер echoServer (порт 33333), ветка feature/dalakov</t>
+          <t>Windows 11, Qt 6.11.1 MinGW 64-bit, сервер echoServer (порт 33333); GUI-прогон — pywinauto (UI Automation)</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -1909,7 +2080,7 @@
           <t>Таймер авторизации срабатывает у вошедшего пользователя</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>Minor</t>
         </is>
@@ -1921,7 +2092,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Windows 11, Qt 6.11.1 MinGW 64-bit, сервер echoServer (порт 33333), ветка feature/dalakov</t>
+          <t>Windows 11, Qt 6.11.1 MinGW 64-bit, сервер echoServer (порт 33333); GUI-прогон — pywinauto (UI Automation)</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -1967,7 +2138,7 @@
           <t>Журнал клиента показывает не то задание, что прислал сервер</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>Trivial</t>
         </is>
@@ -1979,7 +2150,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Windows 11, Qt 6.11.1 MinGW 64-bit, сервер echoServer (порт 33333), ветка feature/dalakov</t>
+          <t>Windows 11, Qt 6.11.1 MinGW 64-bit, сервер echoServer (порт 33333); GUI-прогон — pywinauto (UI Automation)</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -2025,7 +2196,7 @@
           <t>Пользователи не сохраняются между перезапусками сервера</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>Major</t>
         </is>
@@ -2037,7 +2208,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Windows 11, Qt 6.11.1 MinGW 64-bit, сервер echoServer (порт 33333), ветка feature/dalakov</t>
+          <t>Windows 11, Qt 6.11.1 MinGW 64-bit, сервер echoServer (порт 33333); GUI-прогон — pywinauto (UI Automation)</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -2106,7 +2277,7 @@
         </is>
       </c>
       <c r="B3" s="8">
-        <f>COUNTA('Тест-кейсы'!A5:A23)</f>
+        <f>COUNTA('Тест-кейсы'!A5:A26)</f>
         <v/>
       </c>
     </row>
@@ -2117,7 +2288,7 @@
         </is>
       </c>
       <c r="B4" s="8">
-        <f>COUNTIF('Тест-кейсы'!I5:I23,"Passed")</f>
+        <f>COUNTIF('Тест-кейсы'!I5:I26,"Passed")</f>
         <v/>
       </c>
     </row>
@@ -2128,7 +2299,7 @@
         </is>
       </c>
       <c r="B5" s="8">
-        <f>COUNTIF('Тест-кейсы'!I5:I23,"Failed")</f>
+        <f>COUNTIF('Тест-кейсы'!I5:I26,"Failed")</f>
         <v/>
       </c>
     </row>
@@ -2139,7 +2310,7 @@
         </is>
       </c>
       <c r="B6" s="8">
-        <f>COUNTIF('Тест-кейсы'!I5:I23,"Not run")</f>
+        <f>COUNTIF('Тест-кейсы'!I5:I26,"Not run")</f>
         <v/>
       </c>
     </row>
